--- a/ksoft/docs/records/Volume_Types_FT0305.xlsx
+++ b/ksoft/docs/records/Volume_Types_FT0305.xlsx
@@ -1829,13 +1829,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEDC6FE4-73CD-47CB-A26B-8045339971CA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E158B1EC-88AB-4D8A-A0AD-DD6F927DA55C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA5B0522-211D-4616-A348-C03337A667D8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF0BE5B0-7141-4551-9ED8-89999AB85B1E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4356A9B-ED74-4E2F-A6C6-6A25F0BFDA73}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5B56932-7BD8-41EC-96CC-77361322316E}"/>
 </file>
--- a/ksoft/docs/records/Volume_Types_FT0305.xlsx
+++ b/ksoft/docs/records/Volume_Types_FT0305.xlsx
@@ -1829,13 +1829,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E158B1EC-88AB-4D8A-A0AD-DD6F927DA55C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEDC6FE4-73CD-47CB-A26B-8045339971CA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF0BE5B0-7141-4551-9ED8-89999AB85B1E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA5B0522-211D-4616-A348-C03337A667D8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5B56932-7BD8-41EC-96CC-77361322316E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4356A9B-ED74-4E2F-A6C6-6A25F0BFDA73}"/>
 </file>